--- a/artfynd/A 20112-2026 artfynd.xlsx
+++ b/artfynd/A 20112-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132844444</v>
       </c>
       <c r="B2" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 20112-2026 artfynd.xlsx
+++ b/artfynd/A 20112-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -798,6 +798,148 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>133646645</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57955</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Långmyren, Långmyren, Vrm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>475864</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6572395</v>
+      </c>
+      <c r="S3" t="n">
+        <v>3</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Färska hack i död tall</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 20112-2026 artfynd.xlsx
+++ b/artfynd/A 20112-2026 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>133646645</v>
       </c>
       <c r="B3" t="n">
-        <v>57955</v>
+        <v>57962</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 20112-2026 artfynd.xlsx
+++ b/artfynd/A 20112-2026 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>133646645</v>
       </c>
       <c r="B3" t="n">
-        <v>57962</v>
+        <v>57972</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 20112-2026 artfynd.xlsx
+++ b/artfynd/A 20112-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,27 +675,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132844444</v>
+        <v>133643458</v>
       </c>
       <c r="B2" t="n">
-        <v>57958</v>
+        <v>57972</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -703,19 +703,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>475852</v>
+        <v>475964</v>
       </c>
       <c r="R2" t="n">
-        <v>6572304</v>
+        <v>6572330</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,27 +745,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>06:23</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>06:23</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringbarkning i tall.</t>
+          <t>Färska hack i död tall.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,15 +777,40 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Jim Hellquist</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jim Hellquist</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -808,7 +824,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -940,6 +956,249 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>132844444</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Långmyren, Långmyren, Vrm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>475852</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6572304</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>06:23</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>06:23</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringbarkning i tall.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>133647254</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58131</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Långmyren, Långmyren, Vrm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>475872</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6572383</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>09:49</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>09:49</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 20112-2026 artfynd.xlsx
+++ b/artfynd/A 20112-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -814,6 +819,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133643458</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -956,6 +966,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133646645</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1082,6 +1097,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132844444</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1199,8 +1219,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133647254</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>